--- a/data/Неделя_20.07-26.07_2026.xlsx
+++ b/data/Неделя_20.07-26.07_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Отделы\Дирекция по организационному развитию и системе менеджмента качества\ОРСМК\Несоответствия\Инструкции и классификаторы\МОЕ\ИИ\Аналитика данных по качеству\Месяц АН\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105FFCA2-3C32-4FF0-8893-909932A15D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55178847-A869-41D8-AFB5-42223124E101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="96">
   <si>
     <t>№ п/п</t>
   </si>
@@ -211,12 +211,6 @@
     <t>(ПФК) Секция прохода СП1-1н (Ц 208.31.01.000 СБ) (снятие фасок)</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Не выявлены</t>
-  </si>
-  <si>
     <t>(ПФК) Карниз К1 (Ц 208.04.00.000 СБ) (снятие фасок)</t>
   </si>
   <si>
@@ -289,9 +283,6 @@
     <t>Бурая ржавчина</t>
   </si>
   <si>
-    <t>ГПЦ(80) Стойка перильная СПО-012</t>
-  </si>
-  <si>
     <t>С00-0000092</t>
   </si>
   <si>
@@ -317,6 +308,9 @@
   </si>
   <si>
     <t>ДО</t>
+  </si>
+  <si>
+    <t>ЦГЦ</t>
   </si>
 </sst>
 </file>
@@ -382,7 +376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -403,9 +397,6 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -719,7 +710,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="11.4" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="1" customWidth="1"/>
@@ -814,7 +805,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G2" s="3">
         <v>3</v>
@@ -870,7 +861,7 @@
         <v>31</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G3" s="3">
         <v>1</v>
@@ -926,7 +917,7 @@
         <v>33</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G4" s="3">
         <v>5</v>
@@ -982,7 +973,7 @@
         <v>35</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G5" s="3">
         <v>5</v>
@@ -1038,7 +1029,7 @@
         <v>37</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G6" s="3">
         <v>2</v>
@@ -1094,7 +1085,7 @@
         <v>46</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G7" s="3">
         <v>16</v>
@@ -1150,7 +1141,7 @@
         <v>53</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G8" s="3">
         <v>12</v>
@@ -1168,7 +1159,7 @@
         <v>56</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -1194,7 +1185,7 @@
         <v>58</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G9" s="3">
         <v>3</v>
@@ -1241,10 +1232,10 @@
         <v>41</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3">
         <v>1</v>
@@ -1282,19 +1273,19 @@
         <v>11</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>41</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G11" s="3">
         <v>2</v>
@@ -1332,19 +1323,19 @@
         <v>13</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>41</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G12" s="3">
         <v>1</v>
@@ -1382,19 +1373,19 @@
         <v>15</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>41</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G13" s="3">
         <v>3</v>
@@ -1432,10 +1423,10 @@
         <v>16</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>41</v>
@@ -1444,7 +1435,7 @@
         <v>61</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G14" s="3">
         <v>5</v>
@@ -1482,19 +1473,19 @@
         <v>52</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>41</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G15" s="3">
         <v>1</v>
@@ -1503,10 +1494,10 @@
         <v>71.25</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>23</v>
@@ -1518,7 +1509,7 @@
         <v>41</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
@@ -1532,19 +1523,19 @@
         <v>53</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>41</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G16" s="3">
         <v>30</v>
@@ -1553,10 +1544,10 @@
         <v>196.5</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K16" s="5" t="s">
         <v>23</v>
@@ -1568,7 +1559,7 @@
         <v>41</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
@@ -1582,19 +1573,19 @@
         <v>54</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G17" s="3">
         <v>1</v>
@@ -1603,10 +1594,10 @@
         <v>112.68</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>23</v>
@@ -1615,10 +1606,10 @@
         <v>40</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
@@ -1632,19 +1623,19 @@
         <v>56</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G18" s="3">
         <v>1</v>
@@ -1653,22 +1644,22 @@
         <v>38.799999999999997</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>23</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
@@ -1682,19 +1673,19 @@
         <v>59</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G19" s="3">
         <v>1</v>
@@ -1703,22 +1694,22 @@
         <v>17.88</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>23</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
@@ -1732,19 +1723,19 @@
         <v>60</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G20" s="3">
         <v>2</v>
@@ -1753,22 +1744,22 @@
         <v>35.76</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>23</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
@@ -1777,99 +1768,55 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="10.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E21" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2</v>
+      </c>
+      <c r="H21" s="8">
+        <v>50.073999999999998</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N21" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="M21" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="N21" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
-        <v>62</v>
-      </c>
-      <c r="B22" s="4" t="s">
+      <c r="Q21" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G22" s="3">
-        <v>2</v>
-      </c>
-      <c r="H22" s="9">
-        <v>50.073999999999998</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M22" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="N22" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="R22" s="5"/>
+      <c r="R21" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/data/Неделя_20.07-26.07_2026.xlsx
+++ b/data/Неделя_20.07-26.07_2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Отделы\Дирекция по организационному развитию и системе менеджмента качества\ОРСМК\Несоответствия\Инструкции и классификаторы\МОЕ\ИИ\Аналитика данных по качеству\Месяц АН\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s.kulikova\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55178847-A869-41D8-AFB5-42223124E101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56338484-7719-4622-87DA-5D5E07BCA3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист_1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист_1!$A$1:$R$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист_1!$A$1:$R$21</definedName>
   </definedNames>
   <calcPr calcId="124519" refMode="R1C1"/>
 </workbook>
@@ -193,9 +193,6 @@
     <t>Отсутствует маркировка с логотипом завода.</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>К00-0000255</t>
   </si>
   <si>
@@ -311,6 +308,9 @@
   </si>
   <si>
     <t>ЦГЦ</t>
+  </si>
+  <si>
+    <t>В работе</t>
   </si>
 </sst>
 </file>
@@ -805,7 +805,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G2" s="3">
         <v>3</v>
@@ -861,7 +861,7 @@
         <v>31</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G3" s="3">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>33</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G4" s="3">
         <v>5</v>
@@ -973,7 +973,7 @@
         <v>35</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G5" s="3">
         <v>5</v>
@@ -1029,7 +1029,7 @@
         <v>37</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G6" s="3">
         <v>2</v>
@@ -1085,7 +1085,7 @@
         <v>46</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G7" s="3">
         <v>16</v>
@@ -1141,7 +1141,7 @@
         <v>53</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G8" s="3">
         <v>12</v>
@@ -1156,10 +1156,10 @@
         <v>55</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -1173,7 +1173,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>19</v>
@@ -1182,10 +1182,10 @@
         <v>41</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G9" s="3">
         <v>3</v>
@@ -1194,10 +1194,10 @@
         <v>238.47</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>23</v>
@@ -1209,7 +1209,7 @@
         <v>41</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
@@ -1223,7 +1223,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>19</v>
@@ -1232,10 +1232,10 @@
         <v>41</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G10" s="3">
         <v>1</v>
@@ -1244,10 +1244,10 @@
         <v>90.81</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>23</v>
@@ -1259,7 +1259,7 @@
         <v>41</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
@@ -1273,19 +1273,19 @@
         <v>11</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>41</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G11" s="3">
         <v>2</v>
@@ -1294,10 +1294,10 @@
         <v>131.30000000000001</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>23</v>
@@ -1309,7 +1309,7 @@
         <v>41</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
@@ -1323,19 +1323,19 @@
         <v>13</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>41</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G12" s="3">
         <v>1</v>
@@ -1344,10 +1344,10 @@
         <v>55.37</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>23</v>
@@ -1359,7 +1359,7 @@
         <v>41</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
@@ -1373,19 +1373,19 @@
         <v>15</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>41</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G13" s="3">
         <v>3</v>
@@ -1394,10 +1394,10 @@
         <v>142.13999999999999</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>23</v>
@@ -1409,7 +1409,7 @@
         <v>41</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
@@ -1423,19 +1423,19 @@
         <v>16</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>41</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G14" s="3">
         <v>5</v>
@@ -1444,10 +1444,10 @@
         <v>397.45</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>23</v>
@@ -1459,7 +1459,7 @@
         <v>41</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
@@ -1473,19 +1473,19 @@
         <v>52</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>41</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G15" s="3">
         <v>1</v>
@@ -1494,10 +1494,10 @@
         <v>71.25</v>
       </c>
       <c r="I15" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>76</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>23</v>
@@ -1509,7 +1509,7 @@
         <v>41</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
@@ -1523,19 +1523,19 @@
         <v>53</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>41</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G16" s="3">
         <v>30</v>
@@ -1544,10 +1544,10 @@
         <v>196.5</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K16" s="5" t="s">
         <v>23</v>
@@ -1559,7 +1559,7 @@
         <v>41</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
@@ -1573,19 +1573,19 @@
         <v>54</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>81</v>
-      </c>
       <c r="F17" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G17" s="3">
         <v>1</v>
@@ -1594,10 +1594,10 @@
         <v>112.68</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>23</v>
@@ -1606,10 +1606,10 @@
         <v>40</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
@@ -1623,19 +1623,19 @@
         <v>56</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G18" s="3">
         <v>1</v>
@@ -1644,22 +1644,22 @@
         <v>38.799999999999997</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>23</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
@@ -1673,19 +1673,19 @@
         <v>59</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D19" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="F19" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G19" s="3">
         <v>1</v>
@@ -1694,22 +1694,22 @@
         <v>17.88</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>23</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
@@ -1723,19 +1723,19 @@
         <v>60</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D20" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="F20" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G20" s="3">
         <v>2</v>
@@ -1744,22 +1744,22 @@
         <v>35.76</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>23</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
@@ -1773,19 +1773,19 @@
         <v>62</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>87</v>
-      </c>
       <c r="F21" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G21" s="3">
         <v>2</v>
@@ -1800,7 +1800,7 @@
         <v>21</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>40</v>
@@ -1809,17 +1809,17 @@
         <v>41</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="R21" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R21" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="portrait"/>
 </worksheet>
